--- a/combined_data.xlsx
+++ b/combined_data.xlsx
@@ -11,12 +11,73 @@
     <sheet name="ML" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="MD" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Theses" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="CAA" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="DaLeT" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Lovaniensia" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Merged" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="202">
+  <si>
+    <t xml:space="preserve">Institutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">institution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15th</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16th</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17th</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18th</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Castle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Falcon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Lily</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Pig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holy Trinity college</t>
+  </si>
+  <si>
+    <t xml:space="preserve">College of Ghent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vaulx College</t>
+  </si>
+  <si>
+    <t xml:space="preserve">College of the Augustinians</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standonck College</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saint Peter's School</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unknown</t>
+  </si>
   <si>
     <t xml:space="preserve">Age Category</t>
   </si>
@@ -24,24 +85,6 @@
     <t xml:space="preserve">category</t>
   </si>
   <si>
-    <t xml:space="preserve">Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15th</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16th</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17th</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18th</t>
-  </si>
-  <si>
     <t xml:space="preserve">type</t>
   </si>
   <si>
@@ -54,45 +97,6 @@
     <t xml:space="preserve">maiorennis</t>
   </si>
   <si>
-    <t xml:space="preserve">unknown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Institutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">institution</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Castle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Falcon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Lily</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Pig</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holy Trinity college</t>
-  </si>
-  <si>
-    <t xml:space="preserve">College of Ghent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vaulx College</t>
-  </si>
-  <si>
-    <t xml:space="preserve">College of the Augustinians</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Standonck College</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saint Peter's School</t>
-  </si>
-  <si>
     <t xml:space="preserve">Wealth Category</t>
   </si>
   <si>
@@ -168,22 +172,37 @@
     <t xml:space="preserve">role</t>
   </si>
   <si>
+    <t xml:space="preserve">total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">author</t>
+  </si>
+  <si>
+    <t xml:space="preserve">printer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">approbator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dedicatee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">publisher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">editor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">translator</t>
+  </si>
+  <si>
     <t xml:space="preserve">commentator</t>
   </si>
   <si>
-    <t xml:space="preserve">printer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">publisher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">translator</t>
-  </si>
-  <si>
     <t xml:space="preserve">corrector</t>
   </si>
   <si>
-    <t xml:space="preserve">editor</t>
+    <t xml:space="preserve">Faculties</t>
   </si>
   <si>
     <t xml:space="preserve">faculty</t>
@@ -195,51 +214,66 @@
     <t xml:space="preserve">Date unknown</t>
   </si>
   <si>
-    <t xml:space="preserve">Other Faculties</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jesuit college</t>
   </si>
   <si>
     <t xml:space="preserve">Roles</t>
   </si>
   <si>
+    <t xml:space="preserve">dissertant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">author - professor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">engraver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">artist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">illustrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">author - original work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bookseller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matriculation - Age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matriculation - Pedagogy/faculty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matriculation - Inscription fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inscription fee</t>
+  </si>
+  <si>
     <t xml:space="preserve">NAth</t>
   </si>
   <si>
-    <t xml:space="preserve">dissertant</t>
-  </si>
-  <si>
     <t xml:space="preserve">praeses</t>
   </si>
   <si>
-    <t xml:space="preserve">author</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dedicatee</t>
-  </si>
-  <si>
     <t xml:space="preserve"/>
   </si>
   <si>
     <t xml:space="preserve">approbation</t>
   </si>
   <si>
-    <t xml:space="preserve">engraver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">other</t>
-  </si>
-  <si>
     <t xml:space="preserve">patron</t>
   </si>
   <si>
     <t xml:space="preserve">Institution</t>
   </si>
   <si>
-    <t xml:space="preserve">Faculties</t>
-  </si>
-  <si>
     <t xml:space="preserve">name_english</t>
   </si>
   <si>
@@ -256,6 +290,342 @@
   </si>
   <si>
     <t xml:space="preserve">Carmelites</t>
+  </si>
+  <si>
+    <t xml:space="preserve">contributor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eulogist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">subject added entry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">censor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">annotator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">addressee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">author - preface</t>
+  </si>
+  <si>
+    <t xml:space="preserve">depicted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">honoree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">compiler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">author (dubious)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">readapted by</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collection owner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collaborator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">woodcutter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">thesis advisor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">responsible party</t>
+  </si>
+  <si>
+    <t xml:space="preserve">printer / publisher unknown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plantijn workshop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Typographia academica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stamperia Camerale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Old University of Leuven</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Birckmann workshop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Etats de Brabant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Willibrordus and Bonifacius College</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viglius College</t>
+  </si>
+  <si>
+    <t xml:space="preserve">College of Arras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oratorians</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staten-Generaal van de Verenigde Nederlandse Staten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Society of Jesus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baglioni workshop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hunneprik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pluckhaen van Lier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Libraires associés</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raad van Brabant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sheldonian Theatre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Societas Minima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baius College</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recollects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tertiaries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Braine-le-Comte: O.P.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Typographia Balleoniana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Academia Societatis Jesu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colégio das Artes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compagnie de la Grande Navire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Congrégation de Saint-Maur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drukarnia Jego Królewskiej Mości i Rzeczpospolitej</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eliot's Court Press</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faculty of law (Vienna)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faculty of law (Wittenberg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faculty of Theology (Douai)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imprenta del Diario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imprenta real</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imprimerie académique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imprimerie des Nations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seminarium Generale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Longhi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metternich workshop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nivelliana workshop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nortoniana workshop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oporiniana workshop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Société typographique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Speranza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stamperia del Popolo Romano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staten van Holland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vrije drukpers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collegium Italorum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">neuen Buchhandlung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sumptibus Societatis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">creator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedagogies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faculty of Theology (Köln)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imprimerie patriotique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Société des Libraires</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staten van Vlaanderen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comin da Trino workshop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Council of Trente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stamperia di S.A.S.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thielmannus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipografia del Seminario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baba workshop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Batavus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stad Brussel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Society of Jesus Brussels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compagnia degli Aspiranti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drukkerij der vrije Brabantse provinciën</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drukkerij van Ernestus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imprimerie de la religion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Komarek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">city of Mechelen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Officine Anisson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holy Congregation of the Vatican Press</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peeters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raad van Vlaanderen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sint Romboutskapittel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tamo Angelo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trouwe Belg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Woelen-Bosch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Totals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dataset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_ps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_ps_att</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">morethan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MBL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OUL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manuale_lovaniensia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">magister_dixit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lovaniensia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">thesis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dalet</t>
   </si>
 </sst>
 </file>
@@ -625,343 +995,343 @@
       <c r="G2" t="s">
         <v>7</v>
       </c>
-      <c r="H2" t="s">
-        <v>8</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>44343</v>
+        <v>22462</v>
       </c>
       <c r="C3" t="n">
-        <v>30.94</v>
+        <v>15.61</v>
       </c>
       <c r="D3" t="n">
-        <v>468</v>
+        <v>1488</v>
       </c>
       <c r="E3" t="n">
-        <v>1206</v>
+        <v>6780</v>
       </c>
       <c r="F3" t="n">
-        <v>23079</v>
+        <v>7611</v>
       </c>
       <c r="G3" t="n">
-        <v>19590</v>
-      </c>
-      <c r="H3" t="s">
-        <v>10</v>
+        <v>6583</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B4" t="n">
-        <v>6709</v>
+        <v>20117</v>
       </c>
       <c r="C4" t="n">
-        <v>4.68</v>
+        <v>13.98</v>
       </c>
       <c r="D4" t="n">
-        <v>66</v>
+        <v>861</v>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>5880</v>
       </c>
       <c r="F4" t="n">
-        <v>1368</v>
+        <v>7900</v>
       </c>
       <c r="G4" t="n">
-        <v>4922</v>
-      </c>
-      <c r="H4" t="s">
-        <v>10</v>
+        <v>5476</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="n">
+        <v>18411</v>
+      </c>
+      <c r="C5" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1636</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4440</v>
+      </c>
+      <c r="F5" t="n">
+        <v>6183</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6152</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="n">
+        <v>22978</v>
+      </c>
+      <c r="C6" t="n">
+        <v>15.97</v>
+      </c>
+      <c r="D6" t="n">
+        <v>903</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5817</v>
+      </c>
+      <c r="F6" t="n">
+        <v>9400</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6858</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="n">
-        <v>92251</v>
-      </c>
-      <c r="C5" t="n">
-        <v>64.37</v>
-      </c>
-      <c r="D5" t="n">
-        <v>23175</v>
-      </c>
-      <c r="E5" t="n">
-        <v>42225</v>
-      </c>
-      <c r="F5" t="n">
-        <v>16797</v>
-      </c>
-      <c r="G5" t="n">
-        <v>10054</v>
-      </c>
-      <c r="H5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>13</v>
+      <c r="B7" t="n">
+        <v>3754</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="D7"/>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2976</v>
+      </c>
+      <c r="G7" t="n">
+        <v>777</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>6</v>
-      </c>
-      <c r="G8" t="s">
-        <v>7</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D8"/>
+      <c r="E8" t="n">
+        <v>52</v>
+      </c>
+      <c r="F8" t="n">
+        <v>28</v>
+      </c>
+      <c r="G8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" t="n">
-        <v>22462</v>
+        <v>141</v>
       </c>
       <c r="C9" t="n">
-        <v>15.61</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1488</v>
-      </c>
-      <c r="E9" t="n">
-        <v>6780</v>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="D9"/>
+      <c r="E9"/>
       <c r="F9" t="n">
-        <v>7611</v>
-      </c>
-      <c r="G9" t="n">
-        <v>6583</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="G9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" t="n">
-        <v>20117</v>
+        <v>476</v>
       </c>
       <c r="C10" t="n">
-        <v>13.98</v>
-      </c>
-      <c r="D10" t="n">
-        <v>861</v>
-      </c>
-      <c r="E10" t="n">
-        <v>5880</v>
-      </c>
+        <v>0.33</v>
+      </c>
+      <c r="D10"/>
+      <c r="E10"/>
       <c r="F10" t="n">
-        <v>7900</v>
+        <v>473</v>
       </c>
       <c r="G10" t="n">
-        <v>5476</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" t="n">
-        <v>18411</v>
+        <v>2255</v>
       </c>
       <c r="C11" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1636</v>
-      </c>
+        <v>1.57</v>
+      </c>
+      <c r="D11"/>
       <c r="E11" t="n">
-        <v>4440</v>
+        <v>2117</v>
       </c>
       <c r="F11" t="n">
-        <v>6183</v>
-      </c>
-      <c r="G11" t="n">
-        <v>6152</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="G11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" t="n">
-        <v>22978</v>
+        <v>50</v>
       </c>
       <c r="C12" t="n">
-        <v>15.97</v>
-      </c>
-      <c r="D12" t="n">
-        <v>903</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="D12"/>
       <c r="E12" t="n">
-        <v>5817</v>
+        <v>43</v>
       </c>
       <c r="F12" t="n">
-        <v>9400</v>
-      </c>
-      <c r="G12" t="n">
-        <v>6858</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="G12"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" t="n">
+        <v>53134</v>
+      </c>
+      <c r="C13" t="n">
+        <v>36.94</v>
+      </c>
+      <c r="D13" t="n">
+        <v>18821</v>
+      </c>
+      <c r="E13" t="n">
+        <v>18927</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6566</v>
+      </c>
+      <c r="G13" t="n">
+        <v>8820</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B13" t="n">
-        <v>3754</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="D13"/>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2976</v>
-      </c>
-      <c r="G13" t="n">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" t="n">
-        <v>80</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="D14"/>
-      <c r="E14" t="n">
-        <v>52</v>
-      </c>
-      <c r="F14" t="n">
-        <v>28</v>
-      </c>
-      <c r="G14"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" t="n">
-        <v>141</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D15"/>
-      <c r="E15"/>
-      <c r="F15" t="n">
-        <v>141</v>
-      </c>
-      <c r="G15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" t="n">
-        <v>476</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="D16"/>
-      <c r="E16"/>
-      <c r="F16" t="n">
-        <v>473</v>
-      </c>
-      <c r="G16" t="n">
+        <v>20</v>
+      </c>
+      <c r="B16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" t="s">
         <v>3</v>
+      </c>
+      <c r="D16" t="s">
+        <v>4</v>
+      </c>
+      <c r="E16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G16" t="s">
+        <v>7</v>
+      </c>
+      <c r="H16" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="n">
+        <v>44338</v>
+      </c>
+      <c r="C17" t="n">
+        <v>30.94</v>
+      </c>
+      <c r="D17" t="n">
+        <v>468</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1206</v>
+      </c>
+      <c r="F17" t="n">
+        <v>23078</v>
+      </c>
+      <c r="G17" t="n">
+        <v>19586</v>
+      </c>
+      <c r="H17" t="s">
         <v>23</v>
       </c>
-      <c r="B17" t="n">
-        <v>2255</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="D17"/>
-      <c r="E17" t="n">
-        <v>2117</v>
-      </c>
-      <c r="F17" t="n">
-        <v>138</v>
-      </c>
-      <c r="G17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>50</v>
+        <v>6708</v>
       </c>
       <c r="C18" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D18"/>
+        <v>4.68</v>
+      </c>
+      <c r="D18" t="n">
+        <v>66</v>
+      </c>
       <c r="E18" t="n">
-        <v>43</v>
+        <v>353</v>
       </c>
       <c r="F18" t="n">
-        <v>7</v>
-      </c>
-      <c r="G18"/>
+        <v>1368</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4921</v>
+      </c>
+      <c r="H18" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>53134</v>
+        <v>92249</v>
       </c>
       <c r="C19" t="n">
-        <v>36.94</v>
+        <v>64.38</v>
       </c>
       <c r="D19" t="n">
-        <v>18821</v>
+        <v>23175</v>
       </c>
       <c r="E19" t="n">
-        <v>18927</v>
+        <v>42225</v>
       </c>
       <c r="F19" t="n">
-        <v>6566</v>
+        <v>16797</v>
       </c>
       <c r="G19" t="n">
-        <v>8820</v>
+        <v>10052</v>
+      </c>
+      <c r="H19" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -1095,7 +1465,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B28" t="n">
         <v>93374</v>
@@ -1192,7 +1562,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B34" t="n">
         <v>753</v>
@@ -1231,7 +1601,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2</v>
@@ -1252,12 +1622,12 @@
         <v>7</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B3" t="n">
         <v>63</v>
@@ -1283,7 +1653,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B4" t="n">
         <v>63</v>
@@ -1309,7 +1679,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B5" t="n">
         <v>58</v>
@@ -1335,7 +1705,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B6" t="n">
         <v>75</v>
@@ -1392,7 +1762,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>2</v>
@@ -1413,7 +1783,7 @@
         <v>7</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
@@ -1501,7 +1871,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>2</v>
@@ -1522,7 +1892,7 @@
         <v>7</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -1624,101 +1994,174 @@
         <v>49</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3"/>
-      <c r="D3"/>
-      <c r="E3"/>
+        <v>538</v>
+      </c>
+      <c r="C3" t="n">
+        <v>33</v>
+      </c>
+      <c r="D3" t="n">
+        <v>318</v>
+      </c>
+      <c r="E3" t="n">
+        <v>184</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B4" t="n">
+        <v>494</v>
+      </c>
+      <c r="C4" t="n">
         <v>36</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>282</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>174</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" t="n">
-        <v>52</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="C5"/>
       <c r="D5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E5"/>
+        <v>20</v>
+      </c>
+      <c r="E5" t="n">
+        <v>62</v>
+      </c>
+      <c r="F5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" t="n">
-        <v>17</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="C6"/>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F6"/>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7"/>
+        <v>55</v>
+      </c>
+      <c r="B7" t="n">
+        <v>59</v>
+      </c>
       <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7"/>
-      <c r="E7"/>
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>52</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B8"/>
-      <c r="C8" t="n">
+        <v>56</v>
+      </c>
+      <c r="B8" t="n">
+        <v>31</v>
+      </c>
+      <c r="C8"/>
+      <c r="D8" t="n">
         <v>16</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>15</v>
       </c>
-      <c r="E8"/>
+      <c r="F8"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" t="n">
+        <v>23</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>17</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10"/>
+      <c r="E10"/>
+      <c r="F10"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11"/>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11"/>
+      <c r="F11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1733,18 +2176,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>5</v>
@@ -1756,12 +2199,12 @@
         <v>7</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B3" t="n">
         <v>93</v>
@@ -1784,7 +2227,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B4" t="n">
         <v>85</v>
@@ -1805,7 +2248,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B5" t="n">
         <v>86</v>
@@ -1826,7 +2269,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B6" t="n">
         <v>139</v>
@@ -1868,111 +2311,703 @@
         <v>2</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="n">
+        <v>15</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+    </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>59</v>
-      </c>
+      <c r="A9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" t="n">
+        <v>15</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>9</v>
+      </c>
+      <c r="G9"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>58</v>
-      </c>
+      <c r="A10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" t="n">
+        <v>10</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="D10"/>
+      <c r="E10"/>
+      <c r="F10" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D11"/>
+      <c r="E11"/>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" t="n">
+        <v>307</v>
+      </c>
+      <c r="C15" t="n">
+        <v>51.17</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>95</v>
+      </c>
+      <c r="F15" t="n">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" t="n">
+        <v>189</v>
+      </c>
+      <c r="C16" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" t="n">
+        <v>81</v>
+      </c>
+      <c r="F16" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" t="n">
+        <v>63</v>
+      </c>
+      <c r="C17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D17"/>
+      <c r="E17" t="n">
+        <v>43</v>
+      </c>
+      <c r="F17" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" t="n">
+        <v>21</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>9</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" t="n">
+        <v>9</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D19"/>
+      <c r="E19" t="n">
+        <v>9</v>
+      </c>
+      <c r="F19"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="D20"/>
+      <c r="E20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D22"/>
+      <c r="E22"/>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D23"/>
+      <c r="E23"/>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D24"/>
+      <c r="E24"/>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B28" t="n">
+        <v>188</v>
+      </c>
+      <c r="C28" t="n">
+        <v>68.36</v>
+      </c>
+      <c r="D28"/>
+      <c r="E28"/>
+      <c r="F28" t="n">
+        <v>48</v>
+      </c>
+      <c r="G28" t="n">
+        <v>140</v>
+      </c>
+      <c r="H28" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>24</v>
+      </c>
+      <c r="B29" t="n">
+        <v>6</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="D29"/>
+      <c r="E29"/>
+      <c r="F29" t="n">
+        <v>4</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>18</v>
+      </c>
+      <c r="B30" t="n">
+        <v>81</v>
+      </c>
+      <c r="C30" t="n">
+        <v>29.45</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>5</v>
+      </c>
+      <c r="F30" t="n">
+        <v>24</v>
+      </c>
+      <c r="G30" t="n">
+        <v>51</v>
+      </c>
+      <c r="H30" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" t="n">
+        <v>51</v>
+      </c>
+      <c r="C34" t="n">
+        <v>18.28</v>
+      </c>
+      <c r="D34"/>
+      <c r="E34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" t="n">
+        <v>14</v>
+      </c>
+      <c r="G34" t="n">
+        <v>35</v>
+      </c>
+      <c r="H34" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57</v>
+      </c>
+      <c r="C35" t="n">
+        <v>20.43</v>
+      </c>
+      <c r="D35"/>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>13</v>
+      </c>
+      <c r="G35" t="n">
+        <v>43</v>
+      </c>
+      <c r="H35" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>10</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57</v>
+      </c>
+      <c r="C36" t="n">
+        <v>20.43</v>
+      </c>
+      <c r="D36"/>
+      <c r="E36"/>
+      <c r="F36" t="n">
+        <v>14</v>
+      </c>
+      <c r="G36" t="n">
+        <v>43</v>
+      </c>
+      <c r="H36" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80</v>
+      </c>
+      <c r="C37" t="n">
+        <v>28.67</v>
+      </c>
+      <c r="D37"/>
+      <c r="E37"/>
+      <c r="F37" t="n">
+        <v>19</v>
+      </c>
+      <c r="G37" t="n">
+        <v>61</v>
+      </c>
+      <c r="H37" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" t="n">
+        <v>10</v>
+      </c>
+      <c r="C38" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="D38"/>
+      <c r="E38"/>
+      <c r="F38" t="n">
+        <v>6</v>
+      </c>
+      <c r="G38" t="n">
+        <v>4</v>
+      </c>
+      <c r="H38" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
         <v>15</v>
       </c>
-      <c r="C11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D11" t="n">
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="D39"/>
+      <c r="E39"/>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39"/>
+      <c r="H39" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>18</v>
+      </c>
+      <c r="B40" t="n">
+        <v>23</v>
+      </c>
+      <c r="C40" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" t="n">
+        <v>9</v>
+      </c>
+      <c r="G40" t="n">
+        <v>11</v>
+      </c>
+      <c r="H40" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E11" t="n">
+      <c r="D43" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G43" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F11" t="n">
-        <v>3</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" t="n">
-        <v>15</v>
-      </c>
-      <c r="C12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="n">
+      <c r="H43" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>27</v>
+      </c>
+      <c r="B44" t="n">
+        <v>53</v>
+      </c>
+      <c r="C44" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="D44"/>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>9</v>
+      </c>
+      <c r="G44" t="n">
+        <v>43</v>
+      </c>
+      <c r="H44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>28</v>
+      </c>
+      <c r="B45" t="n">
+        <v>20</v>
+      </c>
+      <c r="C45" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="D45"/>
+      <c r="E45" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" t="n">
+        <v>18</v>
+      </c>
+      <c r="G45"/>
+      <c r="H45" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>29</v>
+      </c>
+      <c r="B46" t="n">
+        <v>6</v>
+      </c>
+      <c r="C46" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="D46"/>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46"/>
+      <c r="G46" t="n">
         <v>5</v>
       </c>
-      <c r="F12" t="n">
-        <v>9</v>
-      </c>
-      <c r="G12"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" t="n">
-        <v>10</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="D13"/>
-      <c r="E13"/>
-      <c r="F13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>60</v>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="D14"/>
-      <c r="E14"/>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14"/>
+      <c r="H46" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>18</v>
+      </c>
+      <c r="B47" t="n">
+        <v>196</v>
+      </c>
+      <c r="C47" t="n">
+        <v>71.27</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="n">
+        <v>49</v>
+      </c>
+      <c r="G47" t="n">
+        <v>145</v>
+      </c>
+      <c r="H47" t="s">
+        <v>77</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1987,7 +3022,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2">
@@ -1998,7 +3033,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>5</v>
@@ -2010,12 +3045,12 @@
         <v>7</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B3" t="n">
         <v>3525</v>
@@ -2038,7 +3073,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="B4" t="n">
         <v>2636</v>
@@ -2061,7 +3096,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="B5" t="n">
         <v>4</v>
@@ -2080,7 +3115,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="B6" t="n">
         <v>3</v>
@@ -2099,7 +3134,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="B7" t="n">
         <v>2</v>
@@ -2116,7 +3151,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="B8" t="n">
         <v>346</v>
@@ -2135,7 +3170,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B9" t="n">
         <v>2</v>
@@ -2152,7 +3187,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -2169,7 +3204,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="B11" t="n">
         <v>5</v>
@@ -2197,7 +3232,7 @@
         <v>2</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>5</v>
@@ -2214,17 +3249,17 @@
         <v>27</v>
       </c>
       <c r="B15" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C15" t="n">
-        <v>12.91</v>
+        <v>12.78</v>
       </c>
       <c r="D15"/>
       <c r="E15" t="n">
         <v>13</v>
       </c>
       <c r="F15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -2251,7 +3286,7 @@
         <v>41</v>
       </c>
       <c r="C17" t="n">
-        <v>5.63</v>
+        <v>5.69</v>
       </c>
       <c r="D17"/>
       <c r="E17" t="n">
@@ -2264,35 +3299,35 @@
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="n">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="C18" t="n">
-        <v>81.32</v>
+        <v>81.39</v>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F18" t="n">
-        <v>539</v>
+        <v>534</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>5</v>
@@ -2306,7 +3341,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B22" t="n">
         <v>122</v>
@@ -2324,7 +3359,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B23" t="n">
         <v>137</v>
@@ -2342,7 +3377,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B24" t="n">
         <v>129</v>
@@ -2360,7 +3395,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B25" t="n">
         <v>146</v>
@@ -2378,7 +3413,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B26" t="n">
         <v>14</v>
@@ -2414,18 +3449,18 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>5</v>
@@ -2437,12 +3472,12 @@
         <v>7</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B31" t="n">
         <v>24</v>
@@ -2524,7 +3559,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B35" t="n">
         <v>1</v>
@@ -2541,7 +3576,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="B36" t="n">
         <v>3</v>
@@ -2558,7 +3593,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B37" t="n">
         <v>3</v>
@@ -2575,7 +3610,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B38" t="n">
         <v>1</v>
@@ -2605,6 +3640,3824 @@
       <c r="F39"/>
       <c r="G39" t="n">
         <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1980</v>
+      </c>
+      <c r="C3" t="n">
+        <v>27.08</v>
+      </c>
+      <c r="D3" t="n">
+        <v>691</v>
+      </c>
+      <c r="E3" t="n">
+        <v>841</v>
+      </c>
+      <c r="F3" t="n">
+        <v>448</v>
+      </c>
+      <c r="G3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1455</v>
+      </c>
+      <c r="C4" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="D4" t="n">
+        <v>548</v>
+      </c>
+      <c r="E4" t="n">
+        <v>626</v>
+      </c>
+      <c r="F4" t="n">
+        <v>280</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" t="n">
+        <v>724</v>
+      </c>
+      <c r="C5" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="D5" t="n">
+        <v>266</v>
+      </c>
+      <c r="E5" t="n">
+        <v>353</v>
+      </c>
+      <c r="F5" t="n">
+        <v>105</v>
+      </c>
+      <c r="G5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" t="n">
+        <v>581</v>
+      </c>
+      <c r="C6" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="D6" t="n">
+        <v>112</v>
+      </c>
+      <c r="E6" t="n">
+        <v>377</v>
+      </c>
+      <c r="F6" t="n">
+        <v>92</v>
+      </c>
+      <c r="G6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" t="n">
+        <v>552</v>
+      </c>
+      <c r="C7" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="D7" t="n">
+        <v>180</v>
+      </c>
+      <c r="E7" t="n">
+        <v>249</v>
+      </c>
+      <c r="F7" t="n">
+        <v>123</v>
+      </c>
+      <c r="G7"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" t="n">
+        <v>280</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="D8" t="n">
+        <v>108</v>
+      </c>
+      <c r="E8" t="n">
+        <v>140</v>
+      </c>
+      <c r="F8" t="n">
+        <v>32</v>
+      </c>
+      <c r="G8"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" t="n">
+        <v>276</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="D9" t="n">
+        <v>98</v>
+      </c>
+      <c r="E9" t="n">
+        <v>131</v>
+      </c>
+      <c r="F9" t="n">
+        <v>47</v>
+      </c>
+      <c r="G9"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B10" t="n">
+        <v>250</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="D10" t="n">
+        <v>76</v>
+      </c>
+      <c r="E10" t="n">
+        <v>158</v>
+      </c>
+      <c r="F10" t="n">
+        <v>16</v>
+      </c>
+      <c r="G10"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" t="n">
+        <v>244</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="D11" t="n">
+        <v>91</v>
+      </c>
+      <c r="E11" t="n">
+        <v>86</v>
+      </c>
+      <c r="F11" t="n">
+        <v>67</v>
+      </c>
+      <c r="G11"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>92</v>
+      </c>
+      <c r="B12" t="n">
+        <v>111</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="D12" t="n">
+        <v>24</v>
+      </c>
+      <c r="E12" t="n">
+        <v>40</v>
+      </c>
+      <c r="F12" t="n">
+        <v>47</v>
+      </c>
+      <c r="G12"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" t="n">
+        <v>108</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="D13" t="n">
+        <v>54</v>
+      </c>
+      <c r="E13" t="n">
+        <v>35</v>
+      </c>
+      <c r="F13" t="n">
+        <v>19</v>
+      </c>
+      <c r="G13"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" t="n">
+        <v>93</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="D14" t="n">
+        <v>35</v>
+      </c>
+      <c r="E14" t="n">
+        <v>39</v>
+      </c>
+      <c r="F14" t="n">
+        <v>19</v>
+      </c>
+      <c r="G14"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" t="n">
+        <v>84</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="D15"/>
+      <c r="E15" t="n">
+        <v>41</v>
+      </c>
+      <c r="F15" t="n">
+        <v>43</v>
+      </c>
+      <c r="G15"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" t="n">
+        <v>81</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>50</v>
+      </c>
+      <c r="F16" t="n">
+        <v>29</v>
+      </c>
+      <c r="G16"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>93</v>
+      </c>
+      <c r="B17" t="n">
+        <v>74</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>51</v>
+      </c>
+      <c r="F17" t="n">
+        <v>18</v>
+      </c>
+      <c r="G17"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" t="n">
+        <v>74</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="D18"/>
+      <c r="E18" t="n">
+        <v>41</v>
+      </c>
+      <c r="F18" t="n">
+        <v>33</v>
+      </c>
+      <c r="G18"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>94</v>
+      </c>
+      <c r="B19" t="n">
+        <v>64</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="D19" t="n">
+        <v>27</v>
+      </c>
+      <c r="E19" t="n">
+        <v>20</v>
+      </c>
+      <c r="F19" t="n">
+        <v>17</v>
+      </c>
+      <c r="G19"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B20" t="n">
+        <v>61</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="D20" t="n">
+        <v>17</v>
+      </c>
+      <c r="E20" t="n">
+        <v>17</v>
+      </c>
+      <c r="F20" t="n">
+        <v>27</v>
+      </c>
+      <c r="G20"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>71</v>
+      </c>
+      <c r="B21" t="n">
+        <v>47</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>33</v>
+      </c>
+      <c r="F21" t="n">
+        <v>11</v>
+      </c>
+      <c r="G21"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" t="n">
+        <v>32</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="D22" t="n">
+        <v>14</v>
+      </c>
+      <c r="E22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" t="n">
+        <v>8</v>
+      </c>
+      <c r="G22"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>96</v>
+      </c>
+      <c r="B23" t="n">
+        <v>30</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="D23" t="n">
+        <v>7</v>
+      </c>
+      <c r="E23" t="n">
+        <v>13</v>
+      </c>
+      <c r="F23" t="n">
+        <v>10</v>
+      </c>
+      <c r="G23"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>97</v>
+      </c>
+      <c r="B24" t="n">
+        <v>26</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="D24"/>
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="n">
+        <v>23</v>
+      </c>
+      <c r="G24"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>98</v>
+      </c>
+      <c r="B25" t="n">
+        <v>15</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D25"/>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="n">
+        <v>12</v>
+      </c>
+      <c r="G25"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>99</v>
+      </c>
+      <c r="B26" t="n">
+        <v>13</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>6</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G26"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>70</v>
+      </c>
+      <c r="B27" t="n">
+        <v>11</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D27"/>
+      <c r="E27"/>
+      <c r="F27"/>
+      <c r="G27" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>80</v>
+      </c>
+      <c r="B28" t="n">
+        <v>10</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D28" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4</v>
+      </c>
+      <c r="G28"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>100</v>
+      </c>
+      <c r="B29" t="n">
+        <v>9</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D29"/>
+      <c r="E29" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4</v>
+      </c>
+      <c r="G29"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>101</v>
+      </c>
+      <c r="B30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>102</v>
+      </c>
+      <c r="B31" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="D31"/>
+      <c r="E31"/>
+      <c r="F31" t="n">
+        <v>5</v>
+      </c>
+      <c r="G31"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>58</v>
+      </c>
+      <c r="B32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32"/>
+      <c r="G32"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>103</v>
+      </c>
+      <c r="B33" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33"/>
+      <c r="G33"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>104</v>
+      </c>
+      <c r="B34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34"/>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>82</v>
+      </c>
+      <c r="B35" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35"/>
+      <c r="G35"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>105</v>
+      </c>
+      <c r="B36" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D36"/>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>59</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37"/>
+      <c r="F37"/>
+      <c r="G37"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>106</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38"/>
+      <c r="F38"/>
+      <c r="G38"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42"/>
+      <c r="B42" t="n">
+        <v>88</v>
+      </c>
+      <c r="C42" t="n">
+        <v>71.54</v>
+      </c>
+      <c r="D42" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" t="n">
+        <v>25</v>
+      </c>
+      <c r="F42" t="n">
+        <v>35</v>
+      </c>
+      <c r="G42" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>27</v>
+      </c>
+      <c r="B43" t="n">
+        <v>22</v>
+      </c>
+      <c r="C43" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="D43"/>
+      <c r="E43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F43" t="n">
+        <v>10</v>
+      </c>
+      <c r="G43" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>28</v>
+      </c>
+      <c r="B44" t="n">
+        <v>11</v>
+      </c>
+      <c r="C44" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="D44"/>
+      <c r="E44" t="n">
+        <v>4</v>
+      </c>
+      <c r="F44" t="n">
+        <v>7</v>
+      </c>
+      <c r="G44"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>29</v>
+      </c>
+      <c r="B45" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="D45"/>
+      <c r="E45" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45"/>
+      <c r="G45"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49"/>
+      <c r="B49" t="n">
+        <v>50</v>
+      </c>
+      <c r="C49" t="n">
+        <v>40.32</v>
+      </c>
+      <c r="D49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" t="n">
+        <v>24</v>
+      </c>
+      <c r="F49" t="n">
+        <v>17</v>
+      </c>
+      <c r="G49" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50" t="n">
+        <v>18</v>
+      </c>
+      <c r="C50" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="D50"/>
+      <c r="E50" t="n">
+        <v>2</v>
+      </c>
+      <c r="F50" t="n">
+        <v>8</v>
+      </c>
+      <c r="G50" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>11</v>
+      </c>
+      <c r="B51" t="n">
+        <v>18</v>
+      </c>
+      <c r="C51" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="D51"/>
+      <c r="E51" t="n">
+        <v>4</v>
+      </c>
+      <c r="F51" t="n">
+        <v>9</v>
+      </c>
+      <c r="G51" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>8</v>
+      </c>
+      <c r="B52" t="n">
+        <v>14</v>
+      </c>
+      <c r="C52" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="D52"/>
+      <c r="E52" t="n">
+        <v>3</v>
+      </c>
+      <c r="F52" t="n">
+        <v>7</v>
+      </c>
+      <c r="G52" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>10</v>
+      </c>
+      <c r="B53" t="n">
+        <v>14</v>
+      </c>
+      <c r="C53" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="D53"/>
+      <c r="E53"/>
+      <c r="F53" t="n">
+        <v>5</v>
+      </c>
+      <c r="G53" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>12</v>
+      </c>
+      <c r="B54" t="n">
+        <v>6</v>
+      </c>
+      <c r="C54" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="D54"/>
+      <c r="E54"/>
+      <c r="F54" t="n">
+        <v>6</v>
+      </c>
+      <c r="G54"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>16</v>
+      </c>
+      <c r="B55" t="n">
+        <v>4</v>
+      </c>
+      <c r="C55" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="D55"/>
+      <c r="E55" t="n">
+        <v>4</v>
+      </c>
+      <c r="F55"/>
+      <c r="G55"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59"/>
+      <c r="B59" t="n">
+        <v>1589</v>
+      </c>
+      <c r="C59" t="n">
+        <v>74.88</v>
+      </c>
+      <c r="D59" t="n">
+        <v>553</v>
+      </c>
+      <c r="E59" t="n">
+        <v>665</v>
+      </c>
+      <c r="F59" t="n">
+        <v>335</v>
+      </c>
+      <c r="G59" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>107</v>
+      </c>
+      <c r="B60" t="n">
+        <v>306</v>
+      </c>
+      <c r="C60" t="n">
+        <v>14.42</v>
+      </c>
+      <c r="D60" t="n">
+        <v>44</v>
+      </c>
+      <c r="E60" t="n">
+        <v>107</v>
+      </c>
+      <c r="F60" t="n">
+        <v>128</v>
+      </c>
+      <c r="G60" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>108</v>
+      </c>
+      <c r="B61" t="n">
+        <v>49</v>
+      </c>
+      <c r="C61" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="D61" t="n">
+        <v>12</v>
+      </c>
+      <c r="E61" t="n">
+        <v>36</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>109</v>
+      </c>
+      <c r="B62" t="n">
+        <v>36</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D62"/>
+      <c r="E62"/>
+      <c r="F62" t="n">
+        <v>34</v>
+      </c>
+      <c r="G62" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>88</v>
+      </c>
+      <c r="B63" t="n">
+        <v>24</v>
+      </c>
+      <c r="C63" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="D63"/>
+      <c r="E63" t="n">
+        <v>24</v>
+      </c>
+      <c r="F63"/>
+      <c r="G63"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>110</v>
+      </c>
+      <c r="B64" t="n">
+        <v>10</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="D64"/>
+      <c r="E64" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" t="n">
+        <v>9</v>
+      </c>
+      <c r="G64"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>86</v>
+      </c>
+      <c r="B65" t="n">
+        <v>9</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="D65"/>
+      <c r="E65"/>
+      <c r="F65" t="n">
+        <v>9</v>
+      </c>
+      <c r="G65"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>111</v>
+      </c>
+      <c r="B66" t="n">
+        <v>8</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D66" t="n">
+        <v>3</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" t="n">
+        <v>3</v>
+      </c>
+      <c r="G66" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>112</v>
+      </c>
+      <c r="B67" t="n">
+        <v>8</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D67" t="n">
+        <v>3</v>
+      </c>
+      <c r="E67" t="n">
+        <v>5</v>
+      </c>
+      <c r="F67"/>
+      <c r="G67"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>113</v>
+      </c>
+      <c r="B68" t="n">
+        <v>8</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D68"/>
+      <c r="E68"/>
+      <c r="F68" t="n">
+        <v>8</v>
+      </c>
+      <c r="G68"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>45</v>
+      </c>
+      <c r="B69" t="n">
+        <v>6</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="n">
+        <v>4</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>114</v>
+      </c>
+      <c r="B70" t="n">
+        <v>4</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="D70"/>
+      <c r="E70" t="n">
+        <v>4</v>
+      </c>
+      <c r="F70"/>
+      <c r="G70"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>85</v>
+      </c>
+      <c r="B71" t="n">
+        <v>3</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71"/>
+      <c r="F71"/>
+      <c r="G71" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>115</v>
+      </c>
+      <c r="B72" t="n">
+        <v>3</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D72"/>
+      <c r="E72" t="n">
+        <v>3</v>
+      </c>
+      <c r="F72"/>
+      <c r="G72"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>116</v>
+      </c>
+      <c r="B73" t="n">
+        <v>3</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D73"/>
+      <c r="E73" t="n">
+        <v>3</v>
+      </c>
+      <c r="F73"/>
+      <c r="G73"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>117</v>
+      </c>
+      <c r="B74" t="n">
+        <v>3</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D74"/>
+      <c r="E74"/>
+      <c r="F74" t="n">
+        <v>3</v>
+      </c>
+      <c r="G74"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>118</v>
+      </c>
+      <c r="B75" t="n">
+        <v>3</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D75"/>
+      <c r="E75"/>
+      <c r="F75" t="n">
+        <v>3</v>
+      </c>
+      <c r="G75"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>119</v>
+      </c>
+      <c r="B76" t="n">
+        <v>2</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="D76"/>
+      <c r="E76"/>
+      <c r="F76" t="n">
+        <v>2</v>
+      </c>
+      <c r="G76"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>120</v>
+      </c>
+      <c r="B77" t="n">
+        <v>2</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="D77"/>
+      <c r="E77"/>
+      <c r="F77" t="n">
+        <v>2</v>
+      </c>
+      <c r="G77"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>121</v>
+      </c>
+      <c r="B78" t="n">
+        <v>2</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="D78"/>
+      <c r="E78"/>
+      <c r="F78" t="n">
+        <v>2</v>
+      </c>
+      <c r="G78"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>122</v>
+      </c>
+      <c r="B79" t="n">
+        <v>2</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="D79"/>
+      <c r="E79"/>
+      <c r="F79" t="n">
+        <v>2</v>
+      </c>
+      <c r="G79"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>123</v>
+      </c>
+      <c r="B80" t="n">
+        <v>2</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="D80"/>
+      <c r="E80"/>
+      <c r="F80" t="n">
+        <v>2</v>
+      </c>
+      <c r="G80"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>124</v>
+      </c>
+      <c r="B81" t="n">
+        <v>2</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="D81"/>
+      <c r="E81"/>
+      <c r="F81" t="n">
+        <v>2</v>
+      </c>
+      <c r="G81"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>125</v>
+      </c>
+      <c r="B82" t="n">
+        <v>2</v>
+      </c>
+      <c r="C82" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="D82"/>
+      <c r="E82" t="n">
+        <v>2</v>
+      </c>
+      <c r="F82"/>
+      <c r="G82"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>126</v>
+      </c>
+      <c r="B83" t="n">
+        <v>2</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="D83"/>
+      <c r="E83" t="n">
+        <v>2</v>
+      </c>
+      <c r="F83"/>
+      <c r="G83"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>40</v>
+      </c>
+      <c r="B84" t="n">
+        <v>1</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D84"/>
+      <c r="E84" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84"/>
+      <c r="G84"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>46</v>
+      </c>
+      <c r="B85" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D85"/>
+      <c r="E85"/>
+      <c r="F85"/>
+      <c r="G85" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>127</v>
+      </c>
+      <c r="B86" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D86"/>
+      <c r="E86" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86"/>
+      <c r="G86"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>128</v>
+      </c>
+      <c r="B87" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D87"/>
+      <c r="E87" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87"/>
+      <c r="G87"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>129</v>
+      </c>
+      <c r="B88" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D88"/>
+      <c r="E88" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88"/>
+      <c r="G88"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>130</v>
+      </c>
+      <c r="B89" t="n">
+        <v>1</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D89"/>
+      <c r="E89"/>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>131</v>
+      </c>
+      <c r="B90" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D90"/>
+      <c r="E90"/>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>132</v>
+      </c>
+      <c r="B91" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D91"/>
+      <c r="E91"/>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>133</v>
+      </c>
+      <c r="B92" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D92"/>
+      <c r="E92"/>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>134</v>
+      </c>
+      <c r="B93" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D93" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93"/>
+      <c r="F93"/>
+      <c r="G93"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>135</v>
+      </c>
+      <c r="B94" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D94"/>
+      <c r="E94"/>
+      <c r="F94" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>136</v>
+      </c>
+      <c r="B95" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D95"/>
+      <c r="E95"/>
+      <c r="F95" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>137</v>
+      </c>
+      <c r="B96" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D96"/>
+      <c r="E96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96"/>
+      <c r="G96"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>138</v>
+      </c>
+      <c r="B97" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D97"/>
+      <c r="E97"/>
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>139</v>
+      </c>
+      <c r="B98" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D98"/>
+      <c r="E98" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98"/>
+      <c r="G98"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>140</v>
+      </c>
+      <c r="B99" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D99"/>
+      <c r="E99" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99"/>
+      <c r="G99"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>141</v>
+      </c>
+      <c r="B100" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D100"/>
+      <c r="E100"/>
+      <c r="F100" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>142</v>
+      </c>
+      <c r="B101" t="n">
+        <v>1</v>
+      </c>
+      <c r="C101" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D101"/>
+      <c r="E101" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101"/>
+      <c r="G101"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>143</v>
+      </c>
+      <c r="B102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D102"/>
+      <c r="E102"/>
+      <c r="F102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>144</v>
+      </c>
+      <c r="B103" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D103"/>
+      <c r="E103"/>
+      <c r="F103" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>145</v>
+      </c>
+      <c r="B104" t="n">
+        <v>1</v>
+      </c>
+      <c r="C104" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D104"/>
+      <c r="E104"/>
+      <c r="F104" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>146</v>
+      </c>
+      <c r="B105" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D105"/>
+      <c r="E105"/>
+      <c r="F105" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>147</v>
+      </c>
+      <c r="B106" t="n">
+        <v>1</v>
+      </c>
+      <c r="C106" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D106"/>
+      <c r="E106"/>
+      <c r="F106" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>148</v>
+      </c>
+      <c r="B107" t="n">
+        <v>1</v>
+      </c>
+      <c r="C107" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D107"/>
+      <c r="E107" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107"/>
+      <c r="G107"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>149</v>
+      </c>
+      <c r="B108" t="n">
+        <v>1</v>
+      </c>
+      <c r="C108" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D108"/>
+      <c r="E108" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108"/>
+      <c r="G108"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>150</v>
+      </c>
+      <c r="B109" t="n">
+        <v>1</v>
+      </c>
+      <c r="C109" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D109" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109"/>
+      <c r="F109"/>
+      <c r="G109"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>151</v>
+      </c>
+      <c r="B110" t="n">
+        <v>1</v>
+      </c>
+      <c r="C110" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D110"/>
+      <c r="E110" t="n">
+        <v>1</v>
+      </c>
+      <c r="F110"/>
+      <c r="G110"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>152</v>
+      </c>
+      <c r="B111" t="n">
+        <v>1</v>
+      </c>
+      <c r="C111" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D111" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111"/>
+      <c r="F111"/>
+      <c r="G111"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>153</v>
+      </c>
+      <c r="B112" t="n">
+        <v>1</v>
+      </c>
+      <c r="C112" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D112" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112"/>
+      <c r="F112"/>
+      <c r="G112"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>154</v>
+      </c>
+      <c r="B113" t="n">
+        <v>1</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D113" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113"/>
+      <c r="F113"/>
+      <c r="G113"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>155</v>
+      </c>
+      <c r="B114" t="n">
+        <v>1</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D114"/>
+      <c r="E114"/>
+      <c r="F114" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>156</v>
+      </c>
+      <c r="B115" t="n">
+        <v>1</v>
+      </c>
+      <c r="C115" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D115" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115"/>
+      <c r="F115"/>
+      <c r="G115"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>157</v>
+      </c>
+      <c r="B116" t="n">
+        <v>1</v>
+      </c>
+      <c r="C116" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D116"/>
+      <c r="E116"/>
+      <c r="F116" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>158</v>
+      </c>
+      <c r="B117" t="n">
+        <v>1</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D117"/>
+      <c r="E117"/>
+      <c r="F117" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>107</v>
+      </c>
+      <c r="B3" t="n">
+        <v>25</v>
+      </c>
+      <c r="C3" t="n">
+        <v>103</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="C5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5"/>
+      <c r="F5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>106</v>
+      </c>
+      <c r="B6" t="n">
+        <v>24.77</v>
+      </c>
+      <c r="C6" t="n">
+        <v>103</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6"/>
+      <c r="F6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>36</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="C7" t="n">
+        <v>34</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7"/>
+      <c r="F7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>18</v>
+      </c>
+      <c r="B8" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="C8" t="n">
+        <v>15</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8"/>
+      <c r="F8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>31</v>
+      </c>
+      <c r="B9" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="C9" t="n">
+        <v>29</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9"/>
+      <c r="F9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>56</v>
+      </c>
+      <c r="B10" t="n">
+        <v>13.08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>52</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10"/>
+      <c r="F10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>12</v>
+      </c>
+      <c r="B11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11"/>
+      <c r="F11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13"/>
+      <c r="E13"/>
+      <c r="F13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>29</v>
+      </c>
+      <c r="B14" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="C14" t="n">
+        <v>29</v>
+      </c>
+      <c r="D14"/>
+      <c r="E14"/>
+      <c r="F14" t="s">
+        <v>49</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2226</v>
+      </c>
+      <c r="C3" t="n">
+        <v>34.43</v>
+      </c>
+      <c r="D3"/>
+      <c r="E3" t="n">
+        <v>1019</v>
+      </c>
+      <c r="F3" t="n">
+        <v>889</v>
+      </c>
+      <c r="G3" t="n">
+        <v>316</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2187</v>
+      </c>
+      <c r="C4" t="n">
+        <v>33.83</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>979</v>
+      </c>
+      <c r="F4" t="n">
+        <v>780</v>
+      </c>
+      <c r="G4" t="n">
+        <v>405</v>
+      </c>
+      <c r="H4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2052</v>
+      </c>
+      <c r="C5" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>902</v>
+      </c>
+      <c r="F5" t="n">
+        <v>716</v>
+      </c>
+      <c r="G5" t="n">
+        <v>416</v>
+      </c>
+      <c r="H5" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9"/>
+      <c r="B9" t="n">
+        <v>105</v>
+      </c>
+      <c r="C9" t="n">
+        <v>72.92</v>
+      </c>
+      <c r="D9" t="n">
+        <v>9</v>
+      </c>
+      <c r="E9" t="n">
+        <v>28</v>
+      </c>
+      <c r="F9" t="n">
+        <v>38</v>
+      </c>
+      <c r="G9" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>21</v>
+      </c>
+      <c r="C10" t="n">
+        <v>14.58</v>
+      </c>
+      <c r="D10"/>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C11" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="D11"/>
+      <c r="E11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="D12"/>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16"/>
+      <c r="B16" t="n">
+        <v>56</v>
+      </c>
+      <c r="C16" t="n">
+        <v>38.62</v>
+      </c>
+      <c r="D16" t="n">
+        <v>8</v>
+      </c>
+      <c r="E16" t="n">
+        <v>25</v>
+      </c>
+      <c r="F16" t="n">
+        <v>17</v>
+      </c>
+      <c r="G16" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" t="n">
+        <v>28</v>
+      </c>
+      <c r="C17" t="n">
+        <v>19.31</v>
+      </c>
+      <c r="D17"/>
+      <c r="E17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>13</v>
+      </c>
+      <c r="G17" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" t="n">
+        <v>17</v>
+      </c>
+      <c r="C18" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="D18"/>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>8</v>
+      </c>
+      <c r="G18" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" t="n">
+        <v>17</v>
+      </c>
+      <c r="C19" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>6</v>
+      </c>
+      <c r="G19" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" t="n">
+        <v>16</v>
+      </c>
+      <c r="C20" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="D20"/>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>8</v>
+      </c>
+      <c r="G20" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" t="n">
+        <v>7</v>
+      </c>
+      <c r="C21" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="D21"/>
+      <c r="E21"/>
+      <c r="F21" t="n">
+        <v>6</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="D22"/>
+      <c r="E22" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22"/>
+      <c r="G22"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26"/>
+      <c r="B26" t="n">
+        <v>1924</v>
+      </c>
+      <c r="C26" t="n">
+        <v>93.31</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>823</v>
+      </c>
+      <c r="F26" t="n">
+        <v>653</v>
+      </c>
+      <c r="G26" t="n">
+        <v>441</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>109</v>
+      </c>
+      <c r="B27" t="n">
+        <v>45</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="D27"/>
+      <c r="E27"/>
+      <c r="F27"/>
+      <c r="G27" t="n">
+        <v>45</v>
+      </c>
+      <c r="H27"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>108</v>
+      </c>
+      <c r="B28" t="n">
+        <v>17</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="D28"/>
+      <c r="E28" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>12</v>
+      </c>
+      <c r="G28"/>
+      <c r="H28"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" t="n">
+        <v>8</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="D29"/>
+      <c r="E29" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29"/>
+      <c r="G29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>88</v>
+      </c>
+      <c r="B30" t="n">
+        <v>7</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="D30"/>
+      <c r="E30"/>
+      <c r="F30" t="n">
+        <v>7</v>
+      </c>
+      <c r="G30"/>
+      <c r="H30"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>112</v>
+      </c>
+      <c r="B31" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="D31"/>
+      <c r="E31" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31"/>
+      <c r="H31"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>111</v>
+      </c>
+      <c r="B32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="D32"/>
+      <c r="E32" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32"/>
+      <c r="G32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>87</v>
+      </c>
+      <c r="B33" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D33"/>
+      <c r="E33"/>
+      <c r="F33"/>
+      <c r="G33" t="n">
+        <v>3</v>
+      </c>
+      <c r="H33"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>116</v>
+      </c>
+      <c r="B34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D34"/>
+      <c r="E34"/>
+      <c r="F34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G34"/>
+      <c r="H34"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>120</v>
+      </c>
+      <c r="B35" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D35"/>
+      <c r="E35"/>
+      <c r="F35"/>
+      <c r="G35" t="n">
+        <v>3</v>
+      </c>
+      <c r="H35"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>161</v>
+      </c>
+      <c r="B36" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D36"/>
+      <c r="E36" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36"/>
+      <c r="G36"/>
+      <c r="H36"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>162</v>
+      </c>
+      <c r="B37" t="n">
+        <v>2</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D37"/>
+      <c r="E37"/>
+      <c r="F37"/>
+      <c r="G37" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>122</v>
+      </c>
+      <c r="B38" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D38"/>
+      <c r="E38"/>
+      <c r="F38"/>
+      <c r="G38" t="n">
+        <v>2</v>
+      </c>
+      <c r="H38"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>163</v>
+      </c>
+      <c r="B39" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D39"/>
+      <c r="E39"/>
+      <c r="F39"/>
+      <c r="G39" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>164</v>
+      </c>
+      <c r="B40" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D40"/>
+      <c r="E40"/>
+      <c r="F40"/>
+      <c r="G40" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D41"/>
+      <c r="E41"/>
+      <c r="F41"/>
+      <c r="G41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>115</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D42"/>
+      <c r="E42"/>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42"/>
+      <c r="H42"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>86</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D43"/>
+      <c r="E43"/>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43"/>
+      <c r="H43"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>127</v>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D44"/>
+      <c r="E44"/>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44"/>
+      <c r="H44"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>114</v>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D45"/>
+      <c r="E45"/>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45"/>
+      <c r="H45"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>165</v>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D46"/>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46"/>
+      <c r="G46"/>
+      <c r="H46"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>166</v>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D47"/>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47"/>
+      <c r="G47"/>
+      <c r="H47"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>110</v>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D48"/>
+      <c r="E48"/>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48"/>
+      <c r="H48"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>167</v>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D49"/>
+      <c r="E49"/>
+      <c r="F49"/>
+      <c r="G49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>168</v>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D50"/>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50"/>
+      <c r="G50"/>
+      <c r="H50"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>169</v>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D51"/>
+      <c r="E51"/>
+      <c r="F51"/>
+      <c r="G51" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>170</v>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D52"/>
+      <c r="E52"/>
+      <c r="F52" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52"/>
+      <c r="H52"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>171</v>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D53"/>
+      <c r="E53"/>
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53"/>
+      <c r="H53"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>130</v>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D54"/>
+      <c r="E54"/>
+      <c r="F54"/>
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>172</v>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D55"/>
+      <c r="E55"/>
+      <c r="F55"/>
+      <c r="G55" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>173</v>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D56"/>
+      <c r="E56"/>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56"/>
+      <c r="H56"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>174</v>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D57"/>
+      <c r="E57"/>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57"/>
+      <c r="H57"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>175</v>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D58"/>
+      <c r="E58"/>
+      <c r="F58"/>
+      <c r="G58" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>176</v>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D59"/>
+      <c r="E59"/>
+      <c r="F59"/>
+      <c r="G59" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>113</v>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D60"/>
+      <c r="E60"/>
+      <c r="F60"/>
+      <c r="G60" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>121</v>
+      </c>
+      <c r="B61" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D61"/>
+      <c r="E61"/>
+      <c r="F61"/>
+      <c r="G61" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>177</v>
+      </c>
+      <c r="B62" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D62"/>
+      <c r="E62"/>
+      <c r="F62"/>
+      <c r="G62" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>178</v>
+      </c>
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D63"/>
+      <c r="E63"/>
+      <c r="F63"/>
+      <c r="G63" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>179</v>
+      </c>
+      <c r="B64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D64"/>
+      <c r="E64" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64"/>
+      <c r="G64"/>
+      <c r="H64"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>180</v>
+      </c>
+      <c r="B65" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D65"/>
+      <c r="E65"/>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65"/>
+      <c r="H65"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>181</v>
+      </c>
+      <c r="B66" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D66"/>
+      <c r="E66"/>
+      <c r="F66"/>
+      <c r="G66" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>182</v>
+      </c>
+      <c r="B67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D67"/>
+      <c r="E67"/>
+      <c r="F67"/>
+      <c r="G67" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>183</v>
+      </c>
+      <c r="B68" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D68"/>
+      <c r="E68"/>
+      <c r="F68"/>
+      <c r="G68" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>184</v>
+      </c>
+      <c r="B69" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D69"/>
+      <c r="E69"/>
+      <c r="F69"/>
+      <c r="G69" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>185</v>
+      </c>
+      <c r="B70" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D70"/>
+      <c r="E70"/>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70"/>
+      <c r="H70"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>186</v>
+      </c>
+      <c r="B71" t="n">
+        <v>1</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D71"/>
+      <c r="E71"/>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71"/>
+      <c r="H71"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>131</v>
+      </c>
+      <c r="B72" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D72"/>
+      <c r="E72"/>
+      <c r="F72"/>
+      <c r="G72" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>187</v>
+      </c>
+      <c r="B73" t="n">
+        <v>1</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D73"/>
+      <c r="E73"/>
+      <c r="F73"/>
+      <c r="G73" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B3" t="n">
+        <v>143295</v>
+      </c>
+      <c r="C3" t="n">
+        <v>143303</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="n">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1401</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1403</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>196</v>
+      </c>
+      <c r="B5" t="n">
+        <v>325</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1377</v>
+      </c>
+      <c r="D5" t="n">
+        <v>509</v>
+      </c>
+      <c r="E5" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>197</v>
+      </c>
+      <c r="B6" t="n">
+        <v>616</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1605</v>
+      </c>
+      <c r="D6" t="n">
+        <v>599</v>
+      </c>
+      <c r="E6" t="n">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>198</v>
+      </c>
+      <c r="B7" t="n">
+        <v>3010</v>
+      </c>
+      <c r="C7" t="n">
+        <v>7311</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2056</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>199</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2386</v>
+      </c>
+      <c r="C8" t="n">
+        <v>6465</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2057</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>200</v>
+      </c>
+      <c r="B9" t="n">
+        <v>2561</v>
+      </c>
+      <c r="C9" t="n">
+        <v>6538</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3154</v>
+      </c>
+      <c r="E9" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>201</v>
+      </c>
+      <c r="B10" t="n">
+        <v>428</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1777</v>
+      </c>
+      <c r="D10" t="n">
+        <v>414</v>
+      </c>
+      <c r="E10" t="n">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
